--- a/Starting_point_NEW.xlsx
+++ b/Starting_point_NEW.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -387,10 +387,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2164,11 +2160,11 @@
       </c>
       <c r="D2">
         <f ca="1">RAND()</f>
-        <v>0.27035127248198476</v>
+        <v>0.5039318180532838</v>
       </c>
       <c r="E2">
         <f ca="1">C2*D2</f>
-        <v>998757.50476038491</v>
+        <v>1861673.0764668419</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2185,11 +2181,11 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D18" ca="1" si="1">RAND()</f>
-        <v>0.82374750869202262</v>
+        <v>0.34903803950922552</v>
       </c>
       <c r="E3">
         <f ca="1">C3*D3</f>
-        <v>68222593.503869325</v>
+        <v>28907256.210869044</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2206,11 +2202,11 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.58197216677238695</v>
+        <v>0.74577401484621297</v>
       </c>
       <c r="E4">
         <f t="shared" ref="E4:E18" ca="1" si="2">C4*D4</f>
-        <v>3790407.4156413712</v>
+        <v>4857255.2394439485</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2227,11 +2223,11 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="1"/>
-        <v>0.24365099253651057</v>
+        <v>0.57136907853438501</v>
       </c>
       <c r="E5">
         <f ca="1">C5*D5</f>
-        <v>437355.4046488282</v>
+        <v>1025611.8883192663</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2248,11 +2244,11 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77603886295108393</v>
+        <v>0.25749101259431073</v>
       </c>
       <c r="E6">
         <f ca="1">C6*D6</f>
-        <v>47237972.278808594</v>
+        <v>15673639.421508066</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2269,11 +2265,11 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83977854107809502</v>
+        <v>0.51354530608589499</v>
       </c>
       <c r="E7">
         <f ca="1">C7*D7</f>
-        <v>1344674.8059016336</v>
+        <v>822301.83435769437</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2290,11 +2286,11 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78407395795504209</v>
+        <v>0.78685416369321848</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="2"/>
-        <v>12163761.047208777</v>
+        <v>12206891.874241289</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2311,11 +2307,11 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89335614837525301</v>
+        <v>0.43392960184386431</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
-        <v>1301302.0812167735</v>
+        <v>632081.05189398234</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2332,11 +2328,11 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93580901309007414</v>
+        <v>0.79966541418543835</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="2"/>
-        <v>59138921.59922225</v>
+        <v>50535258.341832519</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2353,7 +2349,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="1"/>
-        <v>0.31293332030954568</v>
+        <v>0.15012876777151851</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="2"/>
@@ -2374,11 +2370,11 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="1"/>
-        <v>0.19736390364392531</v>
+        <v>0.21541191359518752</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="2"/>
-        <v>4133739.9323468185</v>
+        <v>4511751.2001494942</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2395,11 +2391,11 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="1"/>
-        <v>0.45176729690594974</v>
+        <v>0.23192169126342443</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="2"/>
-        <v>49514030.279608928</v>
+        <v>25418789.103067711</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2416,11 +2412,11 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="1"/>
-        <v>0.98482961664104418</v>
+        <v>0.3266290164351453</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="2"/>
-        <v>4675037.8251410713</v>
+        <v>1550525.0662861604</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2437,11 +2433,11 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="1"/>
-        <v>0.43868478702599667</v>
+        <v>0.40112196006686418</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="2"/>
-        <v>6525716.1037079347</v>
+        <v>5966945.0862541674</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2458,11 +2454,11 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5070613982824055E-2</v>
+        <v>0.57653629438488752</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="2"/>
-        <v>3495.0179278209557</v>
+        <v>133704.21982880979</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2479,11 +2475,11 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="1"/>
-        <v>0.18962409232298427</v>
+        <v>0.78850148129831277</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="2"/>
-        <v>6754362.9221749734</v>
+        <v>28086226.302351695</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2500,11 +2496,11 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9577469847529797</v>
+        <v>0.99257132858368236</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="2"/>
-        <v>38501484.582995132</v>
+        <v>39901425.233767875</v>
       </c>
     </row>
   </sheetData>
@@ -2546,7 +2542,7 @@
       </c>
       <c r="D2">
         <f ca="1">RAND()</f>
-        <v>0.89426960692987123</v>
+        <v>0.45004819692188314</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2562,7 +2558,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D13" ca="1" si="1">RAND()</f>
-        <v>0.14213996265432316</v>
+        <v>0.19565409380378918</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2578,7 +2574,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="1"/>
-        <v>8.6255816151831533E-2</v>
+        <v>0.12589448331023623</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2594,7 +2590,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="1"/>
-        <v>0.37914838496360848</v>
+        <v>0.95448712032993543</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2610,7 +2606,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>1.7858633285423586E-3</v>
+        <v>0.49764010967017291</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2626,7 +2622,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78940326849705678</v>
+        <v>0.48250568955586892</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2642,7 +2638,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="1"/>
-        <v>0.56321705168496394</v>
+        <v>0.1525638342285025</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2658,7 +2654,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39486012355704825</v>
+        <v>0.45319375961697006</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2674,7 +2670,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.98304633444705702</v>
+        <v>0.8007619125896166</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2690,7 +2686,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="1"/>
-        <v>0.32696787781713776</v>
+        <v>0.19547375964702973</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2706,7 +2702,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76070442003430705</v>
+        <v>0.8894139050865254</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2722,7 +2718,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="1"/>
-        <v>0.63249786137992137</v>
+        <v>0.92744209933848232</v>
       </c>
     </row>
   </sheetData>
